--- a/data/trans_dic/IP16B_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores vacunados de la triple vírica</t>
+          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,1; 96,76</t>
+          <t>87,14; 96,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,15; 93,92</t>
+          <t>83,51; 94,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,42; 94,4</t>
+          <t>87,41; 94,39</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>92,99; 98,42</t>
+          <t>92,94; 98,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>97,41; 99,8</t>
+          <t>97,33; 99,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,14; 98,89</t>
+          <t>96,04; 98,83</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>98,85; 100,0</t>
+          <t>98,89; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>96,95; 99,83</t>
+          <t>96,36; 99,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98,14; 99,81</t>
+          <t>98,12; 99,8</t>
         </is>
       </c>
     </row>
@@ -726,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>97,47; 99,67</t>
+          <t>97,45; 99,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98,46; 99,75</t>
+          <t>98,46; 99,73</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>97,5; 99,04</t>
+          <t>97,54; 99,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97,3; 98,86</t>
+          <t>97,35; 98,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,72; 98,83</t>
+          <t>97,66; 98,78</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>52215</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>54363</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>106577</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>48764; 54256</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50664; 57209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>101940; 110089</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>151670</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>177047</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>328716</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>146133; 154682</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>173947; 178362</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>322642; 332017</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>172693</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>206484</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>379179</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>171146; 173072</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>201117; 208357</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>374614; 381039</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>271076</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>299288</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>570363</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>267905; 271768</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>294758; 301528</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>565382; 572708</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>647654</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>737181</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1384834</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>641840; 651686</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>730668; 741879</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1375720; 1391436</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,14; 96,95</t>
+          <t>87,1; 97,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,51; 94,3</t>
+          <t>83,46; 94,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,41; 94,39</t>
+          <t>86,87; 94,4</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>92,94; 98,38</t>
+          <t>92,99; 98,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>97,33; 99,8</t>
+          <t>97,22; 99,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,04; 98,83</t>
+          <t>96,31; 98,9</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>98,89; 100,0</t>
+          <t>98,87; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>96,36; 99,83</t>
+          <t>96,63; 99,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98,12; 99,8</t>
+          <t>98,07; 99,8</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>98,58; 100,0</t>
+          <t>98,71; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>97,45; 99,68</t>
+          <t>97,46; 99,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98,46; 99,73</t>
+          <t>98,53; 99,75</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>97,54; 99,04</t>
+          <t>97,54; 99,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97,35; 98,84</t>
+          <t>97,28; 98,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,66; 98,78</t>
+          <t>97,68; 98,79</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>48764; 54256</t>
+          <t>48741; 54285</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50664; 57209</t>
+          <t>50634; 57106</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101940; 110089</t>
+          <t>101318; 110095</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>146133; 154682</t>
+          <t>146217; 154909</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>173947; 178362</t>
+          <t>173740; 178357</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>322642; 332017</t>
+          <t>323542; 332261</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>171146; 173072</t>
+          <t>171120; 173072</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>201117; 208357</t>
+          <t>201685; 208347</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>374614; 381039</t>
+          <t>374432; 381047</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>267905; 271768</t>
+          <t>268274; 271768</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>294758; 301528</t>
+          <t>294795; 301245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>565382; 572708</t>
+          <t>565781; 572832</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>641840; 651686</t>
+          <t>641857; 651919</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>730668; 741879</t>
+          <t>730188; 741701</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1375720; 1391436</t>
+          <t>1375972; 1391602</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16B_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,1; 97,01</t>
+          <t>83,52; 94,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,46; 94,13</t>
+          <t>87,4; 96,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,87; 94,4</t>
+          <t>87,8; 94,66</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>92,99; 98,52</t>
+          <t>97,38; 99,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>97,22; 99,8</t>
+          <t>92,85; 98,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,31; 98,9</t>
+          <t>96,01; 98,85</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>98,87; 100,0</t>
+          <t>96,76; 99,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>96,63; 99,82</t>
+          <t>98,88; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98,07; 99,8</t>
+          <t>98,1; 99,83</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>98,71; 100,0</t>
+          <t>97,54; 99,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>97,46; 99,59</t>
+          <t>98,26; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98,53; 99,75</t>
+          <t>98,43; 99,73</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>97,54; 99,07</t>
+          <t>97,42; 98,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97,28; 98,82</t>
+          <t>97,54; 99,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,68; 98,79</t>
+          <t>97,85; 98,89</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>98</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52215</t>
+          <t>44931</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54363</t>
+          <t>47402</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106577</t>
+          <t>92333</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>48741; 54285</t>
+          <t>41697; 47019</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50634; 57106</t>
+          <t>44295; 49063</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101318; 110095</t>
+          <t>88333; 95236</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>247</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>151670</t>
+          <t>153402</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>177047</t>
+          <t>138642</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>328716</t>
+          <t>292044</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>146217; 154909</t>
+          <t>150794; 154543</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>173740; 178357</t>
+          <t>133353; 141484</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>323542; 332261</t>
+          <t>286544; 295032</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>232</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>172693</t>
+          <t>194222</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>206484</t>
+          <t>174334</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>379179</t>
+          <t>368556</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>171120; 173072</t>
+          <t>190045; 196099</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>201685; 208347</t>
+          <t>172710; 174672</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>374432; 381047</t>
+          <t>364036; 370434</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>337</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>271076</t>
+          <t>286412</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>299288</t>
+          <t>252042</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>570363</t>
+          <t>538453</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>268274; 271768</t>
+          <t>282302; 288450</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>294795; 301245</t>
+          <t>248408; 252813</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>565781; 572832</t>
+          <t>533715; 540731</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>914</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>647654</t>
+          <t>678968</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>737181</t>
+          <t>612419</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1384834</t>
+          <t>1291387</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>641857; 651919</t>
+          <t>672766; 683176</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>730188; 741701</t>
+          <t>606483; 616045</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1375972; 1391602</t>
+          <t>1284136; 1297813</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16B_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>90,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>93,53%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>91,78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>83,52; 94,18</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>87,4; 96,81</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>87,8; 94,66</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>97,38; 99,81</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>92,85; 98,51</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>96,01; 98,85</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>96,76; 99,85</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>98,88; 100,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>98,1; 99,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>97,54; 99,67</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>98,26; 100,0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>98,43; 99,73</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>98,49%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>97,42; 98,93</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>97,54; 99,08</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>97,85; 98,89</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8999605758031968</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9353205632841248</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9177731400066358</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>44931</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>47402</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>92333</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.8351702380933977</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.8740123025370371</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8780141356667081</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>41697; 47019</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>44295; 49063</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>88333; 95236</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9417766520204238</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9680895344799602</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9466259635443547</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9906897494962469</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9653331070868625</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.978488182945101</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>153402</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>138642</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>292044</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.973843289630517</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.9285077642044914</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.9600583853383002</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>150794; 154543</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>133353; 141484</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>286544; 295032</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9980554829837895</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.985122397755302</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9884981079702683</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9888995090563895</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9980635414906353</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9932132037351811</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>194222</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>174334</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>368556</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.9676333448897226</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.9887679736127396</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.9810329165530195</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>190045; 196099</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>172710; 174672</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>364036; 370434</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9984582804909738</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9982750400425151</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9896475627011495</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9969484986116524</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9930516546636339</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>286412</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>252042</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>538453</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.9754470931262568</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.9825755643121322</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.984312580455843</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>282302; 288450</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>248408; 252813</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>533715; 540731</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9966885557127524</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9972519886805289</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1855</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.9831845533667184</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.984936061310289</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9840144001567201</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>678968</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>612419</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1291387</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.9742045800160193</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.9753881255881106</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.9784892211521231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>672766; 683176</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>606483; 616045</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1284136; 1297813</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.989278034787609</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.9907666452958105</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9889110041734674</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>44931</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>47402</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>92333</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>41697</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>44295</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>88333</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>47019</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>49063</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>95236</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>247</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>153402</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>138642</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>292044</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>150794</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>133353</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>286544</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>154543</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>141484</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>295032</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>237</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>232</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>194222</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>174334</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>368556</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>190045</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>172710</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>364036</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>196099</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>174672</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>370434</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>334</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>337</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>286412</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>252042</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>538453</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>282302</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>248408</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>533715</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>288450</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>252813</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>540731</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>941</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>914</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>678968</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>612419</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1291387</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>672766</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>606483</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1284136</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>683176</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>616045</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1297813</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>